--- a/p6_deployment/data/usa/missing/data_understanding/df_match_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,6921 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>23.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Boiko S.
+ (Ukr)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BMO Stadium
+ (Los Angeles, CA)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>22 146</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>cherundolo steve</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>gonzalez luchi</t>
+        </is>
+      </c>
+      <c r="BE2" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>23.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unkel T.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Providence Park
+ (Portland, OR)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25 218</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>22 471</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>neville phil</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>sartini vanni</t>
+        </is>
+      </c>
+      <c r="BE3" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Badawi M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lumen Field
+ (Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>72 000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>30 093</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>schmetzer brian</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>luccin peter</t>
+        </is>
+      </c>
+      <c r="BE4" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23.06.2024 01:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mendoza R.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dick's Sporting Goods Park
+ (Commerce City, CO)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18 061</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>15 583</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>CF Montreal</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>armas chris</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>courtois laurent</t>
+        </is>
+      </c>
+      <c r="BE5" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23.06.2024 01:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Marrufo J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>America First Field
+ (Sandy, UT)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20 213</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>21 570</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Los Angeles Galaxy</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>mastroeni pablo</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>vanney greg</t>
+        </is>
+      </c>
+      <c r="BE6" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fischer D.
+ (Can)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Allianz Field
+ (Saint Paul, MN)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>19 400</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19 746</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Austin FC</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>ramsay eric</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>wolff josh</t>
+        </is>
+      </c>
+      <c r="BE7" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>23.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Rivas V.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Geodis Park
+ (Nashville, TN)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>29 663</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>munthali rumba</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>cushing nicholas</t>
+        </is>
+      </c>
+      <c r="BE8" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>23.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dujic F.
+ (Can)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CITYPARK
+ (St. Louis, MO)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>22 423</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Atlanta Utd</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>carnell bradley</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>valentino rob</t>
+        </is>
+      </c>
+      <c r="BE9" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>De Oliveira M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Lower.com Field
+ (Columbus, OH)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20 371</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20 818</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>nancy wilfried</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>vermes peter</t>
+        </is>
+      </c>
+      <c r="BE10" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ford T.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Audi Field
+ (Washington, DC)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>17 993</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DC United</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>lesesne troy</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>olsen ben</t>
+        </is>
+      </c>
+      <c r="BE11" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Freemon J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TQL Stadium
+ (Cincinnati, OH)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>25 513</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>noonan pat</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>porter caleb</t>
+        </is>
+      </c>
+      <c r="BE12" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dickerson J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Harrison, NJ)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>New York Red Bulls</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Toronto FC</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>schwarz sandro</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>herdman john</t>
+        </is>
+      </c>
+      <c r="BE13" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Simon N.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Inter&amp;Co Stadium
+ (Orlando, FL)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>25 500</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>22 038</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>pareja oscar</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>klopas frank</t>
+        </is>
+      </c>
+      <c r="BE14" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Da Silva A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Subaru Park
+ (Chester, PA)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>18 500</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>18 762</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>curtin jim</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>smith dean</t>
+        </is>
+      </c>
+      <c r="BE15" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W4YFmVG3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>23.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wiseman T.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cashman Field
+ (Las Vegas, NV)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>12 500</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1 657</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>vVWDE67k</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>MoS88xdH</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>zDeq7OqE</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>sanchez dennis</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>S2Oqee3l</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>glass stephen</t>
+        </is>
+      </c>
+      <c r="BE16" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>KU63vRwj</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>23.06.2024 02:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ndiaye A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Wild Horse Pass Stadium
+ (Chandler, AZ)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CWnNB64j</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2wA8p3yn</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Charleston</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>McXMYtMJ</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>stone danny</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>zPVO4eiP</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>pirmann ben</t>
+        </is>
+      </c>
+      <c r="BE17" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0pQWqmGS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>23.06.2024 01:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Corbyn M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rio Grande Credit Union Field at Isotopes Park
+ (Albuquerque, NM)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10 176</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>dI5p0xzH</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>rmLxuq9b</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Cf83muss</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>quill eric</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>chambers james</t>
+        </is>
+      </c>
+      <c r="BE18" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>plz8kini</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>23.06.2024 00:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Matto J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ONEOK Field
+ (Tulsa, OK)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>7 833</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3 433</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OEz4Fa6C</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FC Tulsa</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>z3BFwb83</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>sanchez mario</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>briggs mark</t>
+        </is>
+      </c>
+      <c r="BE19" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>AeXJnkW9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>23.06.2024 00:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Johnston K.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lynn Family Stadium
+ (Louisville, KY)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>15 304</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>nRGIlQ2T</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Louisville City</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>IorPEfz8</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>cruz danny</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>smith khano</t>
+        </is>
+      </c>
+      <c r="BE20" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2gCbu7Oq</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Hassan M.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>WakeMed Soccer Park
+ (Cary, NC)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1 996</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OnB4oqMu</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>trYG3CIh</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>0YXKhAXq</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>bradford john</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>j7eIjow4</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>lilley bob</t>
+        </is>
+      </c>
+      <c r="BE21" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>OvZBlB1c</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Surgan J.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Michael A. Carroll Stadium
+ (Indianapolis, IN)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>12 111</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>9 490</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>llkqyHYq</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>mcauley sean</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>MRdhQQTs</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>karlsen morten</t>
+        </is>
+      </c>
+      <c r="BE22" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hKMOo9oG</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22.06.2024 23:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tattersall E.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Riccardo Silva Stadium
+ (Miami, FL)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>UJTiXUTf</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>faQG6GQT</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Loudoun</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>zVUAOJSG</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>nocerino antonio</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>tvIcCmLN</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>martin ryan</t>
+        </is>
+      </c>
+      <c r="BE23" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>6NQSpT0M</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>22.06.2024 22:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Montero R.
+ (Cos)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cardinale Stadium
+ (Seaside, CA)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>6 000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4 330</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0vY9Fnhq</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>zLYVwGMm</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>xKVirYma</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>yallop frank</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>A7iCSGMH</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>glinton gavin</t>
+        </is>
+      </c>
+      <c r="BE24" t="n">
+        <v>167</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/p6_deployment/data/usa/missing/data_understanding/df_match_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,865 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>clearances_completed_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>COgk2UVd</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26.06.2024 20:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bensalah N.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Beirne Stadium
+ (Pawtucket, RI)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5 252</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3 481</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EabuZlYo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>MRumD0sn</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>El Paso</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>n9nYS6gm</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>smith khano</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>U31kqHhr</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>cabrera wilmer</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>167</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>bL57wogd</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26.06.2024 20:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ndiaye A.
+ (Usa)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Keyworth Stadium
+ (Hamtramck, MI)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7 933</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6 244</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>dAoaDOc7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>rysqEtSu</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>lKNscApp</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>dichio danny</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>v7f8zS64</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>soehn tom</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>167</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1673</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>